--- a/ZCloud-电力监管-001-20261020/powercor-2020-capex-reconciliation/targets/answer.xlsx
+++ b/ZCloud-电力监管-001-20261020/powercor-2020-capex-reconciliation/targets/answer.xlsx
@@ -1,24 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Working" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Working" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Results'!$A$1:$D$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Working'!$A$1:$F$21</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.000000000"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,13 +32,40 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00172B4D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00172B4D"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0017365D"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -47,8 +80,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -412,101 +472,102 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="110" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>source_note</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="90" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>2020 network net capex difference</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="9" t="n">
         <v>13.69010834417945</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>AUD million nominal</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Powercor_RFM_inputs.xlsx, 'RFM input'!F61:F62, F64, F115:F116, F118, F169:F170, F172, L7:L8, L10 and F282:F287 (network classes F7:F8, F10); Distribution_handbook.pdf, p. 27, section 2.4.1 and footnote 20 (2020 reconciliation).</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2020 non-network net capex difference</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="9" t="n">
         <v>-11.54610040608111</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>AUD million nominal</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Powercor_RFM_inputs.xlsx, 'RFM input'!F65:F67, F119:F121, F173:F175, L11:L13 and F282:F287 (non-network classes F11:F13); Distribution_handbook.pdf, p. 27, section 2.4.1 and footnote 20 (2020 reconciliation).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2020 total net capex difference</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="9" t="n">
         <v>1.143185786329452</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>AUD million nominal</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Powercor_RFM_inputs.xlsx, 'RFM input'!F61:F110, F115:F164, F169:F218, L7:L56 and F282:F287 (all named asset classes F7:F56); Distribution_handbook.pdf, p. 27, section 2.4.1 and footnote 20 (2020 reconciliation).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -514,389 +575,451 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="53" customWidth="1" min="6" max="6"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="112" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Asset class</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Actual net capex</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>2020 forecast</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Year-end difference</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Subtransmission</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>network</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="6" t="n">
         <v>5.647659440000001</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="6" t="n">
         <v>3.430646381427779</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="6" t="n">
         <v>2.356718893154099</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Powercor_RFM_inputs.xlsx, 'RFM input'!F7 (asset class), F60 (year), F61 (capex), F115 (asset disposals), F169 (capital contributions), L7 (2020 forecast net capex), F282, F284 and F287 (inflation and WACC); Distribution_handbook.pdf, p. 27, section 2.4.1 and footnote 20.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="58" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Distribution system assets</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>network</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="6" t="n">
         <v>285.85551699</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="6" t="n">
         <v>279.6600947254131</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="6" t="n">
         <v>13.26661414419533</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Powercor_RFM_inputs.xlsx, 'RFM input'!F8 (asset class), F60 (year), F62 (capex), F116 (asset disposals), F170 (capital contributions), L8 (2020 forecast net capex), F282, F284 and F287 (inflation and WACC); Distribution_handbook.pdf, p. 27, section 2.4.1 and footnote 20.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="58" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Public lighting</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="C4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Powercor_RFM_inputs.xlsx, 'RFM input'!F9 (asset class), F60 (year), F63 (capex), F117 (asset disposals), F171 (capital contributions), L9 (2020 forecast net capex), F282, F284 and F287 (inflation and WACC); Distribution_handbook.pdf, p. 27, section 2.4.1 and footnote 20.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>SCADA/Network control</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>network</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="6" t="n">
         <v>20.18786627</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>22.62047707800938</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="6" t="n">
         <v>-1.933224693169978</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Powercor_RFM_inputs.xlsx, 'RFM input'!F10 (asset class), F60 (year), F64 (capex), F118 (asset disposals), F172 (capital contributions), L10 (2020 forecast net capex), F282, F284 and F287 (inflation and WACC); Distribution_handbook.pdf, p. 27, section 2.4.1 and footnote 20.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Non-network general assets - IT</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>non-network</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="6" t="n">
         <v>34.80915085</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>36.86465196632263</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="6" t="n">
         <v>-1.194429105474592</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Powercor_RFM_inputs.xlsx, 'RFM input'!F11 (asset class), F60 (year), F65 (capex), F119 (asset disposals), F173 (capital contributions), L11 (2020 forecast net capex), F282, F284 and F287 (inflation and WACC); Distribution_handbook.pdf, p. 27, section 2.4.1 and footnote 20.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Non-network general assets - Other</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>non-network</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="6" t="n">
         <v>42.47485407</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>42.52701479772985</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="6" t="n">
         <v>0.9985373534194599</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Powercor_RFM_inputs.xlsx, 'RFM input'!F12 (asset class), F60 (year), F66 (capex), F120 (asset disposals), F174 (capital contributions), L12 (2020 forecast net capex), F282, F284 and F287 (inflation and WACC); Distribution_handbook.pdf, p. 27, section 2.4.1 and footnote 20.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>VBRC</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>non-network</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="6" t="n">
         <v>13.71430507</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>25.40376371880166</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="6" t="n">
         <v>-11.35020865402598</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Powercor_RFM_inputs.xlsx, 'RFM input'!F13 (asset class), F60 (year), F67 (capex), F121 (asset disposals), F175 (capital contributions), L13 (2020 forecast net capex), F282, F284 and F287 (inflation and WACC); Distribution_handbook.pdf, p. 27, section 2.4.1 and footnote 20.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Land</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="C9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6" t="n">
         <v>1.000822151768884</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="6" t="n">
         <v>-1.000822151768884</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Powercor_RFM_inputs.xlsx, 'RFM input'!F14 (asset class), F60 (year), F68 (capex), F122 (asset disposals), F176 (capital contributions), L14 (2020 forecast net capex), F282, F284 and F287 (inflation and WACC); Distribution_handbook.pdf, p. 27, section 2.4.1 and footnote 20.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Accelerated depreciation assets</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="C10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Powercor_RFM_inputs.xlsx, 'RFM input'!F15 (asset class), F60 (year), F69 (capex), F123 (asset disposals), F177 (capital contributions), L15 (2020 forecast net capex), F282, F284 and F287 (inflation and WACC); Distribution_handbook.pdf, p. 27, section 2.4.1 and footnote 20.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Old SWER ACRs</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="C11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Powercor_RFM_inputs.xlsx, 'RFM input'!F16 (asset class), F60 (year), F70 (capex), F124 (asset disposals), F178 (capital contributions), L16 (2020 forecast net capex), F282, F284 and F287 (inflation and WACC); Distribution_handbook.pdf, p. 27, section 2.4.1 and footnote 20.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>in-house software</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="C12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Powercor_RFM_inputs.xlsx, 'RFM input'!F55 (asset class), F60 (year), F109 (capex), F163 (asset disposals), F217 (capital contributions), L55 (2020 forecast net capex), F282, F284 and F287 (inflation and WACC); Distribution_handbook.pdf, p. 27, section 2.4.1 and footnote 20.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Equity raising costs</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="C13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Powercor_RFM_inputs.xlsx, 'RFM input'!F56 (asset class), F60 (year), F110 (capex), F164 (asset disposals), F218 (capital contributions), L56 (2020 forecast net capex), F282, F284 and F287 (inflation and WACC); Distribution_handbook.pdf, p. 27, section 2.4.1 and footnote 20.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Applicable rate</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="7" t="n">
         <v>0.05008580413845843</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Powercor_RFM_inputs.xlsx, 'RFM input'!F281:F284 and F287; Distribution_handbook.pdf, p. 27, section 2.4.1, footnote 20.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Year-end factor</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="7" t="n">
         <v>1.024736943873138</v>
       </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>sqrt(1 + applicable rate). The factor grosses up actual net capex only; forecast is already at year end. Distribution_handbook.pdf, p. 27, section 2.4.1 and footnotes 19-20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="23" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Calculation and scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="35" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Actual net capex = gross capex - asset disposals - capital contributions. Year-end difference = actual net capex x year-end factor - 2020 forecast net capex. All capex figures are nominal AUD million.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="35" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Applicable rate = (1 + F287) / (1 + F284) x (1 + F282) - 1; year-end factor = sqrt(1 + applicable rate). Inputs are Powercor_RFM_inputs.xlsx, RFM input; policy is Distribution_handbook.pdf, p. 27, section 2.4.1 / footnotes 19-20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="35" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>All 12 named asset classes are included in the total, including Land. Land contributes -1.000822151768884; therefore the total is not just network plus non-network. Results displays 0.000 while underlying full-precision values are retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="35" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>The Results interface contains exactly the four requested columns and the three requested labels in order. Each result retains a source reference. Supporting worksheets may be organized freely; static values and cached formulas are both permitted by the task.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="5">
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>